--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/63.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/63.xlsx
@@ -426,13 +426,13 @@
         <v>-3.561190353231322</v>
       </c>
       <c r="E2">
-        <v>-5.510788137647806</v>
+        <v>-7.065866111881807</v>
       </c>
       <c r="F2">
-        <v>-4.084450352681294</v>
+        <v>-4.174232125266316</v>
       </c>
       <c r="G2">
-        <v>-10.05620366548805</v>
+        <v>-12.74457189719969</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.53453239235381</v>
       </c>
       <c r="E3">
-        <v>-5.47658910194188</v>
+        <v>-7.226414100875743</v>
       </c>
       <c r="F3">
-        <v>-4.05414038941286</v>
+        <v>-4.03527680691631</v>
       </c>
       <c r="G3">
-        <v>-9.832427339761017</v>
+        <v>-12.18082571840828</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.627789587210692</v>
       </c>
       <c r="E4">
-        <v>-6.744231245487019</v>
+        <v>-8.762748721191997</v>
       </c>
       <c r="F4">
-        <v>-4.017186091206572</v>
+        <v>-4.194817055225884</v>
       </c>
       <c r="G4">
-        <v>-9.637942720965452</v>
+        <v>-12.028388338507</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.81530633540087</v>
       </c>
       <c r="E5">
-        <v>-7.655514183946556</v>
+        <v>-8.802019647786514</v>
       </c>
       <c r="F5">
-        <v>-4.173654753186565</v>
+        <v>-3.912712394365498</v>
       </c>
       <c r="G5">
-        <v>-9.30876193581356</v>
+        <v>-11.77517133129922</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.056667342738323</v>
       </c>
       <c r="E6">
-        <v>-8.256415513920366</v>
+        <v>-10.17089582777312</v>
       </c>
       <c r="F6">
-        <v>-4.085147838034452</v>
+        <v>-3.888894346432804</v>
       </c>
       <c r="G6">
-        <v>-9.4697438337517</v>
+        <v>-11.49230507824174</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.313039372368256</v>
       </c>
       <c r="E7">
-        <v>-8.536442761132678</v>
+        <v>-10.28043055707066</v>
       </c>
       <c r="F7">
-        <v>-3.41590649984312</v>
+        <v>-3.66959153184826</v>
       </c>
       <c r="G7">
-        <v>-9.402360989845375</v>
+        <v>-11.36700092958032</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.541589105959745</v>
       </c>
       <c r="E8">
-        <v>-9.733866386714881</v>
+        <v>-11.11966547406816</v>
       </c>
       <c r="F8">
-        <v>-3.22466794449802</v>
+        <v>-3.199454097491609</v>
       </c>
       <c r="G8">
-        <v>-9.632016844450156</v>
+        <v>-11.51273445476458</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.709377836430741</v>
       </c>
       <c r="E9">
-        <v>-9.962463754622082</v>
+        <v>-10.41040681803881</v>
       </c>
       <c r="F9">
-        <v>-3.447175712563995</v>
+        <v>-3.404188414563118</v>
       </c>
       <c r="G9">
-        <v>-9.772443565134962</v>
+        <v>-11.53629229682203</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.791216624285141</v>
       </c>
       <c r="E10">
-        <v>-10.25788781346047</v>
+        <v>-10.70932685881112</v>
       </c>
       <c r="F10">
-        <v>-2.602930991755032</v>
+        <v>-2.704014180816447</v>
       </c>
       <c r="G10">
-        <v>-10.30941736215029</v>
+        <v>-11.83889933293019</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.773523727003682</v>
       </c>
       <c r="E11">
-        <v>-10.64593727965175</v>
+        <v>-11.3449796983198</v>
       </c>
       <c r="F11">
-        <v>-2.333448993378505</v>
+        <v>-2.668059722065337</v>
       </c>
       <c r="G11">
-        <v>-11.09882356708058</v>
+        <v>-12.1116849748206</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.662616011773399</v>
       </c>
       <c r="E12">
-        <v>-11.90079101259923</v>
+        <v>-10.93248552943511</v>
       </c>
       <c r="F12">
-        <v>-2.340230837305225</v>
+        <v>-2.443131464448382</v>
       </c>
       <c r="G12">
-        <v>-10.90255125369381</v>
+        <v>-12.76200854055503</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.472444625948903</v>
       </c>
       <c r="E13">
-        <v>-12.2833429113452</v>
+        <v>-12.62439587428488</v>
       </c>
       <c r="F13">
-        <v>-2.147757186162551</v>
+        <v>-1.987454839842402</v>
       </c>
       <c r="G13">
-        <v>-10.36016471472178</v>
+        <v>-11.97989215690221</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.231822407218708</v>
       </c>
       <c r="E14">
-        <v>-12.40175797817177</v>
+        <v>-12.59489739459891</v>
       </c>
       <c r="F14">
-        <v>-2.200694005038454</v>
+        <v>-1.776804322780099</v>
       </c>
       <c r="G14">
-        <v>-10.69369224616673</v>
+        <v>-11.3734564933819</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.975723718451769</v>
       </c>
       <c r="E15">
-        <v>-12.97398953920302</v>
+        <v>-14.19414157582972</v>
       </c>
       <c r="F15">
-        <v>-1.200499180243649</v>
+        <v>-1.485775659889354</v>
       </c>
       <c r="G15">
-        <v>-9.223081706711683</v>
+        <v>-11.46847246090452</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.735279614928046</v>
       </c>
       <c r="E16">
-        <v>-13.87028775717118</v>
+        <v>-14.57175743790733</v>
       </c>
       <c r="F16">
-        <v>-1.058184832075291</v>
+        <v>-1.160875882265541</v>
       </c>
       <c r="G16">
-        <v>-9.810044741370003</v>
+        <v>-11.12579789213456</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.545595056861341</v>
       </c>
       <c r="E17">
-        <v>-13.8002186788505</v>
+        <v>-15.19056888258148</v>
       </c>
       <c r="F17">
-        <v>-0.9633790111922907</v>
+        <v>-0.9464538084182913</v>
       </c>
       <c r="G17">
-        <v>-8.859232888672544</v>
+        <v>-10.77265537836943</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.429702675063297</v>
       </c>
       <c r="E18">
-        <v>-15.38699597113819</v>
+        <v>-15.25730953250652</v>
       </c>
       <c r="F18">
-        <v>-0.5828767283903659</v>
+        <v>-0.2941144787136806</v>
       </c>
       <c r="G18">
-        <v>-9.468816881000704</v>
+        <v>-10.34550561907388</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.402785240448289</v>
       </c>
       <c r="E19">
-        <v>-15.99945396677957</v>
+        <v>-16.96599787355471</v>
       </c>
       <c r="F19">
-        <v>-0.2812665002962603</v>
+        <v>-0.1047248394116296</v>
       </c>
       <c r="G19">
-        <v>-8.519147166514294</v>
+        <v>-10.77486351224412</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.477571351948034</v>
       </c>
       <c r="E20">
-        <v>-17.92675439054805</v>
+        <v>-17.19328198399969</v>
       </c>
       <c r="F20">
-        <v>-0.3061663960570106</v>
+        <v>0.1814926656036555</v>
       </c>
       <c r="G20">
-        <v>-8.640640877260006</v>
+        <v>-10.02579961525539</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.650931226146768</v>
       </c>
       <c r="E21">
-        <v>-18.24688127509828</v>
+        <v>-17.88402823828568</v>
       </c>
       <c r="F21">
-        <v>0.1498332918360612</v>
+        <v>0.170967429383685</v>
       </c>
       <c r="G21">
-        <v>-7.966077497087031</v>
+        <v>-9.187963439631094</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.921155744962077</v>
       </c>
       <c r="E22">
-        <v>-18.11013041701465</v>
+        <v>-17.96273311653899</v>
       </c>
       <c r="F22">
-        <v>0.5661260166433416</v>
+        <v>0.475959881583421</v>
       </c>
       <c r="G22">
-        <v>-8.179147518540065</v>
+        <v>-9.333733380816284</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.275902183472903</v>
       </c>
       <c r="E23">
-        <v>-19.62753601597884</v>
+        <v>-18.74190235429875</v>
       </c>
       <c r="F23">
-        <v>0.9132691157671275</v>
+        <v>0.7285547820864771</v>
       </c>
       <c r="G23">
-        <v>-7.708331663581533</v>
+        <v>-9.43490696304195</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.693182431031711</v>
       </c>
       <c r="E24">
-        <v>-19.06776228694269</v>
+        <v>-19.85173170715058</v>
       </c>
       <c r="F24">
-        <v>0.7700327946794538</v>
+        <v>0.6157187163141423</v>
       </c>
       <c r="G24">
-        <v>-7.895248375274324</v>
+        <v>-9.00915094341844</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.155036770656806</v>
       </c>
       <c r="E25">
-        <v>-19.68610277032004</v>
+        <v>-19.86330648671419</v>
       </c>
       <c r="F25">
-        <v>0.7241561511776117</v>
+        <v>0.708917504435712</v>
       </c>
       <c r="G25">
-        <v>-7.175446390307208</v>
+        <v>-9.003400525816726</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.630981475923069</v>
       </c>
       <c r="E26">
-        <v>-20.1594505729198</v>
+        <v>-19.77167734364299</v>
       </c>
       <c r="F26">
-        <v>0.7178274242202234</v>
+        <v>0.7883413710161286</v>
       </c>
       <c r="G26">
-        <v>-7.618705264196844</v>
+        <v>-8.759707958125434</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.096323551454695</v>
       </c>
       <c r="E27">
-        <v>-20.12712632545305</v>
+        <v>-20.45217113277561</v>
       </c>
       <c r="F27">
-        <v>0.775824739559828</v>
+        <v>0.9753801036290345</v>
       </c>
       <c r="G27">
-        <v>-7.334230086007271</v>
+        <v>-8.246791895543993</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.527125329310979</v>
       </c>
       <c r="E28">
-        <v>-19.84209058598826</v>
+        <v>-20.52919141869807</v>
       </c>
       <c r="F28">
-        <v>0.5663612729857367</v>
+        <v>0.9031597199833624</v>
       </c>
       <c r="G28">
-        <v>-7.557152290985176</v>
+        <v>-9.274997681858533</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.89627157355013</v>
       </c>
       <c r="E29">
-        <v>-20.75248594354229</v>
+        <v>-20.50212472955423</v>
       </c>
       <c r="F29">
-        <v>0.5426558830198231</v>
+        <v>0.612604883247019</v>
       </c>
       <c r="G29">
-        <v>-7.319196898713441</v>
+        <v>-9.262437472082539</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.187577862344514</v>
       </c>
       <c r="E30">
-        <v>-20.50862308975523</v>
+        <v>-20.70960129468965</v>
       </c>
       <c r="F30">
-        <v>0.6411139757817668</v>
+        <v>0.5490293418169626</v>
       </c>
       <c r="G30">
-        <v>-7.524023661773689</v>
+        <v>-9.292401219758482</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.383801763067225</v>
       </c>
       <c r="E31">
-        <v>-20.58613697934453</v>
+        <v>-21.18106525210222</v>
       </c>
       <c r="F31">
-        <v>0.3108836539209383</v>
+        <v>0.522188581231453</v>
       </c>
       <c r="G31">
-        <v>-7.745816970722701</v>
+        <v>-8.938252300149408</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.477476784243985</v>
       </c>
       <c r="E32">
-        <v>-20.29338472017066</v>
+        <v>-20.30610520365821</v>
       </c>
       <c r="F32">
-        <v>0.2131545244734582</v>
+        <v>0.4282318369363219</v>
       </c>
       <c r="G32">
-        <v>-7.574334022333993</v>
+        <v>-8.984371510056995</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.471578880229441</v>
       </c>
       <c r="E33">
-        <v>-20.13732444891832</v>
+        <v>-19.33047717802368</v>
       </c>
       <c r="F33">
-        <v>-0.1931613433345049</v>
+        <v>0.3494681791759365</v>
       </c>
       <c r="G33">
-        <v>-6.430037335593829</v>
+        <v>-8.686650839164798</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.368118539851915</v>
       </c>
       <c r="E34">
-        <v>-20.15754861383658</v>
+        <v>-20.90401321231295</v>
       </c>
       <c r="F34">
-        <v>0.2593045292182243</v>
+        <v>0.1757843858309641</v>
       </c>
       <c r="G34">
-        <v>-7.256008516005372</v>
+        <v>-8.605502746906183</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.180110087329671</v>
       </c>
       <c r="E35">
-        <v>-20.34072991592085</v>
+        <v>-20.35854946114103</v>
       </c>
       <c r="F35">
-        <v>0.2551303858755176</v>
+        <v>0.00336468114266384</v>
       </c>
       <c r="G35">
-        <v>-7.270339867644877</v>
+        <v>-8.352030827691884</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.921043317729572</v>
       </c>
       <c r="E36">
-        <v>-19.96087245920945</v>
+        <v>-20.50546674337189</v>
       </c>
       <c r="F36">
-        <v>0.004614687553488294</v>
+        <v>-0.09857586818064892</v>
       </c>
       <c r="G36">
-        <v>-6.865079435454994</v>
+        <v>-8.66370213748657</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.607689761801681</v>
       </c>
       <c r="E37">
-        <v>-18.69813012454061</v>
+        <v>-19.49120177750392</v>
       </c>
       <c r="F37">
-        <v>0.08003091263916089</v>
+        <v>0.04394225836879762</v>
       </c>
       <c r="G37">
-        <v>-6.613742818113526</v>
+        <v>-8.071303187052767</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.265440152045703</v>
       </c>
       <c r="E38">
-        <v>-18.6602811387845</v>
+        <v>-19.4199326535712</v>
       </c>
       <c r="F38">
-        <v>-0.1810174772094641</v>
+        <v>-0.01536719093684138</v>
       </c>
       <c r="G38">
-        <v>-6.602675664375742</v>
+        <v>-8.093712269808092</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.909960163150986</v>
       </c>
       <c r="E39">
-        <v>-17.5983539839858</v>
+        <v>-19.27849935336364</v>
       </c>
       <c r="F39">
-        <v>-0.3090250919640717</v>
+        <v>0.03510357818092689</v>
       </c>
       <c r="G39">
-        <v>-6.142321133321309</v>
+        <v>-7.219549477981379</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.561535441828264</v>
       </c>
       <c r="E40">
-        <v>-18.63681458647675</v>
+        <v>-18.28194524933967</v>
       </c>
       <c r="F40">
-        <v>-0.2995369717324062</v>
+        <v>-0.3071248171420496</v>
       </c>
       <c r="G40">
-        <v>-5.930628298812612</v>
+        <v>-7.275722814691732</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.234333005493738</v>
       </c>
       <c r="E41">
-        <v>-17.14644850581236</v>
+        <v>-18.56805876561829</v>
       </c>
       <c r="F41">
-        <v>-0.3191982720378524</v>
+        <v>-0.296563132756356</v>
       </c>
       <c r="G41">
-        <v>-5.830007577692005</v>
+        <v>-7.281224941378</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.934418188097172</v>
       </c>
       <c r="E42">
-        <v>-17.87143908054435</v>
+        <v>-17.89598340966593</v>
       </c>
       <c r="F42">
-        <v>-0.3432813975394425</v>
+        <v>-0.2199805663675417</v>
       </c>
       <c r="G42">
-        <v>-6.075623572341613</v>
+        <v>-6.791783957215531</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.669584861980212</v>
       </c>
       <c r="E43">
-        <v>-17.30157591141911</v>
+        <v>-18.74935169404137</v>
       </c>
       <c r="F43">
-        <v>-0.2852111858683916</v>
+        <v>-0.2894988155452818</v>
       </c>
       <c r="G43">
-        <v>-5.780912187344613</v>
+        <v>-7.287435524809673</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.435508933985581</v>
       </c>
       <c r="E44">
-        <v>-16.36966124538063</v>
+        <v>-18.00832579284821</v>
       </c>
       <c r="F44">
-        <v>-0.8356232201281343</v>
+        <v>-0.4604639070742662</v>
       </c>
       <c r="G44">
-        <v>-5.681933496811483</v>
+        <v>-6.710228667855585</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.230044124070375</v>
       </c>
       <c r="E45">
-        <v>-16.56067227902417</v>
+        <v>-17.40014720514408</v>
       </c>
       <c r="F45">
-        <v>-0.4338749701792076</v>
+        <v>-0.502561538484537</v>
       </c>
       <c r="G45">
-        <v>-5.483539123734039</v>
+        <v>-6.808118188906294</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.047084456857434</v>
       </c>
       <c r="E46">
-        <v>-16.18081482231276</v>
+        <v>-17.17554395131164</v>
       </c>
       <c r="F46">
-        <v>-0.8564467198997082</v>
+        <v>-0.5562761943516682</v>
       </c>
       <c r="G46">
-        <v>-5.999053964563809</v>
+        <v>-6.639743842778961</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.874838122049963</v>
       </c>
       <c r="E47">
-        <v>-15.8100731837788</v>
+        <v>-17.1259254616096</v>
       </c>
       <c r="F47">
-        <v>-0.7259921078372309</v>
+        <v>-0.6522160502091013</v>
       </c>
       <c r="G47">
-        <v>-5.521792477440318</v>
+        <v>-7.03489386889191</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.707567186821375</v>
       </c>
       <c r="E48">
-        <v>-16.28902723720005</v>
+        <v>-16.67980284474395</v>
       </c>
       <c r="F48">
-        <v>-1.17665296781926</v>
+        <v>-0.8628980452327107</v>
       </c>
       <c r="G48">
-        <v>-5.987261801352926</v>
+        <v>-6.725728642070452</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.533989283979703</v>
       </c>
       <c r="E49">
-        <v>-14.6798973972105</v>
+        <v>-16.19968950197674</v>
       </c>
       <c r="F49">
-        <v>-1.357285935306317</v>
+        <v>-0.9607332057077491</v>
       </c>
       <c r="G49">
-        <v>-5.763998610184476</v>
+        <v>-6.639237329311453</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.347654190073293</v>
       </c>
       <c r="E50">
-        <v>-14.6609457334884</v>
+        <v>-15.79689532441648</v>
       </c>
       <c r="F50">
-        <v>-0.9230714817394696</v>
+        <v>-0.8824334336929315</v>
       </c>
       <c r="G50">
-        <v>-5.460702980604147</v>
+        <v>-6.3096129310573</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.146167561005753</v>
       </c>
       <c r="E51">
-        <v>-15.45542574186809</v>
+        <v>-16.09072988887818</v>
       </c>
       <c r="F51">
-        <v>-1.41216693247659</v>
+        <v>-1.202843459993572</v>
       </c>
       <c r="G51">
-        <v>-6.273402183948751</v>
+        <v>-5.93281987995961</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.925221704519994</v>
       </c>
       <c r="E52">
-        <v>-14.65989059904461</v>
+        <v>-14.76246506379235</v>
       </c>
       <c r="F52">
-        <v>-1.196881699795624</v>
+        <v>-1.244275084011992</v>
       </c>
       <c r="G52">
-        <v>-5.031139833610474</v>
+        <v>-6.550253175761383</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.687703338716549</v>
       </c>
       <c r="E53">
-        <v>-14.01245014169397</v>
+        <v>-14.82893853375095</v>
       </c>
       <c r="F53">
-        <v>-1.628543125027043</v>
+        <v>-1.501595820548019</v>
       </c>
       <c r="G53">
-        <v>-5.623058754941084</v>
+        <v>-5.642451930710134</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.433490215171706</v>
       </c>
       <c r="E54">
-        <v>-14.28649527474215</v>
+        <v>-14.68847885545503</v>
       </c>
       <c r="F54">
-        <v>-1.452209384360515</v>
+        <v>-1.345272122863516</v>
       </c>
       <c r="G54">
-        <v>-5.295198877459362</v>
+        <v>-6.639416098770574</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.165225546004919</v>
       </c>
       <c r="E55">
-        <v>-13.75325387491695</v>
+        <v>-14.46390277246665</v>
       </c>
       <c r="F55">
-        <v>-1.567726047048309</v>
+        <v>-1.472356936331405</v>
       </c>
       <c r="G55">
-        <v>-5.23266267222253</v>
+        <v>-5.973652148640981</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.890633420062729</v>
       </c>
       <c r="E56">
-        <v>-13.87574003987641</v>
+        <v>-14.00172671524381</v>
       </c>
       <c r="F56">
-        <v>-1.432408089963996</v>
+        <v>-1.504681489123447</v>
       </c>
       <c r="G56">
-        <v>-5.321004579937981</v>
+        <v>-6.173615720304039</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.615198386923353</v>
       </c>
       <c r="E57">
-        <v>-14.02871642032953</v>
+        <v>-14.65018155077217</v>
       </c>
       <c r="F57">
-        <v>-1.709165639239311</v>
+        <v>-1.274754034230597</v>
       </c>
       <c r="G57">
-        <v>-5.823671193529839</v>
+        <v>-5.811127536481541</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.349769543839526</v>
       </c>
       <c r="E58">
-        <v>-13.20673951777526</v>
+        <v>-14.48625532016851</v>
       </c>
       <c r="F58">
-        <v>-1.526382229974586</v>
+        <v>-1.424362985748007</v>
       </c>
       <c r="G58">
-        <v>-6.731568444401727</v>
+        <v>-6.14240720750533</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.104502828834829</v>
       </c>
       <c r="E59">
-        <v>-12.72822925480675</v>
+        <v>-13.91353921241844</v>
       </c>
       <c r="F59">
-        <v>-1.823882099016001</v>
+        <v>-1.555249177227343</v>
       </c>
       <c r="G59">
-        <v>-5.849036593451735</v>
+        <v>-6.715168001800177</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.8859046419449876</v>
       </c>
       <c r="E60">
-        <v>-12.24995900096066</v>
+        <v>-13.79184553041031</v>
       </c>
       <c r="F60">
-        <v>-1.376887593158762</v>
+        <v>-1.639707860881975</v>
       </c>
       <c r="G60">
-        <v>-6.195412352134601</v>
+        <v>-6.415172986122501</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.7027071222575888</v>
       </c>
       <c r="E61">
-        <v>-13.32120122679313</v>
+        <v>-13.56771323787468</v>
       </c>
       <c r="F61">
-        <v>-1.503361071483385</v>
+        <v>-1.312542498411505</v>
       </c>
       <c r="G61">
-        <v>-6.177230836032924</v>
+        <v>-6.834926986683312</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.5587821075208304</v>
       </c>
       <c r="E62">
-        <v>-13.53705546884275</v>
+        <v>-13.60571166327304</v>
       </c>
       <c r="F62">
-        <v>-1.492807670771719</v>
+        <v>-1.726911754109485</v>
       </c>
       <c r="G62">
-        <v>-6.268436365639845</v>
+        <v>-7.514191341522054</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.4569179978338124</v>
       </c>
       <c r="E63">
-        <v>-11.96881322066845</v>
+        <v>-13.7431916056719</v>
       </c>
       <c r="F63">
-        <v>-1.812104371282997</v>
+        <v>-1.51999800240121</v>
       </c>
       <c r="G63">
-        <v>-5.960158365022912</v>
+        <v>-7.254853135612167</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.3980164107060604</v>
       </c>
       <c r="E64">
-        <v>-11.47636431470434</v>
+        <v>-13.89732727547098</v>
       </c>
       <c r="F64">
-        <v>-1.642945120692116</v>
+        <v>-1.600619688246075</v>
       </c>
       <c r="G64">
-        <v>-5.869525559794284</v>
+        <v>-6.576115157514169</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.3784166971197592</v>
       </c>
       <c r="E65">
-        <v>-12.33129945108643</v>
+        <v>-13.64657661271825</v>
       </c>
       <c r="F65">
-        <v>-1.589422646062434</v>
+        <v>-1.395617808503462</v>
       </c>
       <c r="G65">
-        <v>-5.759112244968512</v>
+        <v>-7.838780400010975</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.3954081663460163</v>
       </c>
       <c r="E66">
-        <v>-11.37982177733481</v>
+        <v>-12.37715025041409</v>
       </c>
       <c r="F66">
-        <v>-1.739380340256423</v>
+        <v>-1.317274133016296</v>
       </c>
       <c r="G66">
-        <v>-6.700134814506347</v>
+        <v>-7.554669381830722</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.4420965391814583</v>
       </c>
       <c r="E67">
-        <v>-12.70413777308595</v>
+        <v>-12.85581900997287</v>
       </c>
       <c r="F67">
-        <v>-1.975768232523706</v>
+        <v>-2.044753013094044</v>
       </c>
       <c r="G67">
-        <v>-6.795306377669315</v>
+        <v>-8.230785407861616</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.5102736806200938</v>
       </c>
       <c r="E68">
-        <v>-12.01786112264553</v>
+        <v>-13.22905130921105</v>
       </c>
       <c r="F68">
-        <v>-1.767597019097982</v>
+        <v>-1.789607569357768</v>
       </c>
       <c r="G68">
-        <v>-6.501922521433563</v>
+        <v>-8.111092633889266</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.5915395705334232</v>
       </c>
       <c r="E69">
-        <v>-11.02211308699492</v>
+        <v>-12.13851325563189</v>
       </c>
       <c r="F69">
-        <v>-1.731578776056857</v>
+        <v>-1.73059136211272</v>
       </c>
       <c r="G69">
-        <v>-6.543357309403081</v>
+        <v>-7.615421203021888</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.6764591167095627</v>
       </c>
       <c r="E70">
-        <v>-11.82054192470931</v>
+        <v>-13.06669193061404</v>
       </c>
       <c r="F70">
-        <v>-1.662458143232461</v>
+        <v>-1.576195275374531</v>
       </c>
       <c r="G70">
-        <v>-6.59314791431372</v>
+        <v>-7.731992132550705</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.7591748343410243</v>
       </c>
       <c r="E71">
-        <v>-12.09912006023916</v>
+        <v>-13.19038719813356</v>
       </c>
       <c r="F71">
-        <v>-1.710587946069918</v>
+        <v>-2.028412637706421</v>
       </c>
       <c r="G71">
-        <v>-6.836598812180645</v>
+        <v>-8.083929607739545</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.8322133683171139</v>
       </c>
       <c r="E72">
-        <v>-11.186283855195</v>
+        <v>-13.26148424005398</v>
       </c>
       <c r="F72">
-        <v>-2.257304633345772</v>
+        <v>-1.931742161799718</v>
       </c>
       <c r="G72">
-        <v>-5.97306618208053</v>
+        <v>-7.658802591768497</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.8895569675956702</v>
       </c>
       <c r="E73">
-        <v>-11.60993618403458</v>
+        <v>-13.26783768908675</v>
       </c>
       <c r="F73">
-        <v>-2.042939716849316</v>
+        <v>-1.72566754627048</v>
       </c>
       <c r="G73">
-        <v>-6.250258160083707</v>
+        <v>-8.023161233820684</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.9259531885445853</v>
       </c>
       <c r="E74">
-        <v>-11.96909851453093</v>
+        <v>-14.12879569589904</v>
       </c>
       <c r="F74">
-        <v>-1.981727507619446</v>
+        <v>-2.122133297291754</v>
       </c>
       <c r="G74">
-        <v>-5.970858048205836</v>
+        <v>-6.986467208743451</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.9361467670652234</v>
       </c>
       <c r="E75">
-        <v>-12.38770159485196</v>
+        <v>-12.49817824674309</v>
       </c>
       <c r="F75">
-        <v>-2.273655777509631</v>
+        <v>-2.047806375340763</v>
       </c>
       <c r="G75">
-        <v>-4.79332017370585</v>
+        <v>-6.947439187380983</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.9160487448837125</v>
       </c>
       <c r="E76">
-        <v>-11.27164106176557</v>
+        <v>-13.15053209839205</v>
       </c>
       <c r="F76">
-        <v>-2.374425015325385</v>
+        <v>-1.886664064474175</v>
       </c>
       <c r="G76">
-        <v>-5.833192322500783</v>
+        <v>-7.271472074219307</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.863230368729389</v>
       </c>
       <c r="E77">
-        <v>-12.12066653956766</v>
+        <v>-14.53525793740551</v>
       </c>
       <c r="F77">
-        <v>-2.279079927263163</v>
+        <v>-2.079234634602976</v>
       </c>
       <c r="G77">
-        <v>-4.998620344778214</v>
+        <v>-6.814732658893758</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.7776570054190985</v>
       </c>
       <c r="E78">
-        <v>-13.67649624048693</v>
+        <v>-14.36439861309611</v>
       </c>
       <c r="F78">
-        <v>-2.785317613033816</v>
+        <v>-2.511569522532872</v>
       </c>
       <c r="G78">
-        <v>-5.275216424584321</v>
+        <v>-6.296655455816593</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.6626158494041395</v>
       </c>
       <c r="E79">
-        <v>-13.97372263198038</v>
+        <v>-15.59417818546311</v>
       </c>
       <c r="F79">
-        <v>-2.45694614762487</v>
+        <v>-2.000908354831269</v>
       </c>
       <c r="G79">
-        <v>-5.323805301464204</v>
+        <v>-6.621549084495127</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.5238351913202886</v>
       </c>
       <c r="E80">
-        <v>-14.04831112736072</v>
+        <v>-15.3087756396037</v>
       </c>
       <c r="F80">
-        <v>-2.596217073955342</v>
+        <v>-2.702361587847862</v>
       </c>
       <c r="G80">
-        <v>-4.764773339520715</v>
+        <v>-6.322507505932761</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.3693578465424275</v>
       </c>
       <c r="E81">
-        <v>-14.67660972508093</v>
+        <v>-16.57903524112527</v>
       </c>
       <c r="F81">
-        <v>-2.748933231600653</v>
+        <v>-2.498878933921983</v>
       </c>
       <c r="G81">
-        <v>-4.379889315125046</v>
+        <v>-6.543337446129845</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.2089836171541137</v>
       </c>
       <c r="E82">
-        <v>-14.60508247812978</v>
+        <v>-16.93412194501472</v>
       </c>
       <c r="F82">
-        <v>-2.508766327241798</v>
+        <v>-2.224669442777679</v>
       </c>
       <c r="G82">
-        <v>-4.2855288356192</v>
+        <v>-5.903624178848778</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.05278762652728789</v>
       </c>
       <c r="E83">
-        <v>-15.3740128361582</v>
+        <v>-17.89068056660295</v>
       </c>
       <c r="F83">
-        <v>-2.889899826004656</v>
+        <v>-2.914682093594209</v>
       </c>
       <c r="G83">
-        <v>-4.589628927765572</v>
+        <v>-5.308053725788352</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.08840698038707603</v>
       </c>
       <c r="E84">
-        <v>-16.99934102767319</v>
+        <v>-18.30518537794704</v>
       </c>
       <c r="F84">
-        <v>-2.780249661263488</v>
+        <v>-2.542564545643421</v>
       </c>
       <c r="G84">
-        <v>-3.773092802140952</v>
+        <v>-5.68317164084317</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.2046006229749803</v>
       </c>
       <c r="E85">
-        <v>-18.29980555082592</v>
+        <v>-18.78437038354268</v>
       </c>
       <c r="F85">
-        <v>-3.054029229725739</v>
+        <v>-2.570660282844171</v>
       </c>
       <c r="G85">
-        <v>-4.632225717219375</v>
+        <v>-6.019688594910086</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.2877960952326342</v>
       </c>
       <c r="E86">
-        <v>-18.25215694731721</v>
+        <v>-20.47085561653126</v>
       </c>
       <c r="F86">
-        <v>-3.219964474384925</v>
+        <v>-2.971131190257981</v>
       </c>
       <c r="G86">
-        <v>-3.551895391389008</v>
+        <v>-4.509497172987514</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.3294873557429838</v>
       </c>
       <c r="E87">
-        <v>-20.41234773235216</v>
+        <v>-21.13064069402681</v>
       </c>
       <c r="F87">
-        <v>-3.351433008148429</v>
+        <v>-3.247338703577837</v>
       </c>
       <c r="G87">
-        <v>-3.767349005630316</v>
+        <v>-5.108841647962708</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.3241095544069705</v>
       </c>
       <c r="E88">
-        <v>-21.23255400156943</v>
+        <v>-23.11158542089014</v>
       </c>
       <c r="F88">
-        <v>-3.35085646443608</v>
+        <v>-3.081056372976879</v>
       </c>
       <c r="G88">
-        <v>-3.64269041334906</v>
+        <v>-4.825852904720268</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.2669199920412116</v>
       </c>
       <c r="E89">
-        <v>-21.5287931857292</v>
+        <v>-24.76283459762504</v>
       </c>
       <c r="F89">
-        <v>-3.617156703618454</v>
+        <v>-3.59918858628433</v>
       </c>
       <c r="G89">
-        <v>-3.176817202880661</v>
+        <v>-5.726625861591644</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.1516105224240647</v>
       </c>
       <c r="E90">
-        <v>-23.6271431297154</v>
+        <v>-25.00999870896369</v>
       </c>
       <c r="F90">
-        <v>-3.772106139781713</v>
+        <v>-3.037350880437774</v>
       </c>
       <c r="G90">
-        <v>-3.631312068330585</v>
+        <v>-5.334892318475224</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.02486949044344654</v>
       </c>
       <c r="E91">
-        <v>-25.35504125750413</v>
+        <v>-27.94805000277018</v>
       </c>
       <c r="F91">
-        <v>-3.690361187738652</v>
+        <v>-3.534512972943356</v>
       </c>
       <c r="G91">
-        <v>-3.434519999294148</v>
+        <v>-4.698814030196275</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.2681483495694397</v>
       </c>
       <c r="E92">
-        <v>-27.46797288779502</v>
+        <v>-30.36916693165308</v>
       </c>
       <c r="F92">
-        <v>-4.076767245020329</v>
+        <v>-3.768409964430421</v>
       </c>
       <c r="G92">
-        <v>-3.585076989329123</v>
+        <v>-5.096973342204421</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.5817927865908139</v>
       </c>
       <c r="E93">
-        <v>-30.2539331178169</v>
+        <v>-30.6711595420396</v>
       </c>
       <c r="F93">
-        <v>-4.04839980331146</v>
+        <v>-3.75401708080678</v>
       </c>
       <c r="G93">
-        <v>-3.771970527203139</v>
+        <v>-5.245318887819163</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.9634361739328577</v>
       </c>
       <c r="E94">
-        <v>-31.46618976001123</v>
+        <v>-32.44075812272796</v>
       </c>
       <c r="F94">
-        <v>-3.930296977592126</v>
+        <v>-4.176339491939038</v>
       </c>
       <c r="G94">
-        <v>-4.422161671116</v>
+        <v>-5.928675076944443</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.411407112067526</v>
       </c>
       <c r="E95">
-        <v>-34.23255301876491</v>
+        <v>-35.20381785969305</v>
       </c>
       <c r="F95">
-        <v>-4.23195110915858</v>
+        <v>-4.027929188053479</v>
       </c>
       <c r="G95">
-        <v>-3.846474354564437</v>
+        <v>-5.79527664443951</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.917591869181545</v>
       </c>
       <c r="E96">
-        <v>-35.56669127463868</v>
+        <v>-37.05673356941153</v>
       </c>
       <c r="F96">
-        <v>-4.464173141757185</v>
+        <v>-4.040177428471272</v>
       </c>
       <c r="G96">
-        <v>-3.876742672429994</v>
+        <v>-6.208462522650408</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.463877912694341</v>
       </c>
       <c r="E97">
-        <v>-37.03571918577893</v>
+        <v>-38.34674411031755</v>
       </c>
       <c r="F97">
-        <v>-4.281939768447919</v>
+        <v>-4.355215492164758</v>
       </c>
       <c r="G97">
-        <v>-5.532243869707797</v>
+        <v>-6.900664489456621</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.040972138496489</v>
       </c>
       <c r="E98">
-        <v>-39.67351227474384</v>
+        <v>-41.26250399082129</v>
       </c>
       <c r="F98">
-        <v>-4.718848901176074</v>
+        <v>-4.452058268491243</v>
       </c>
       <c r="G98">
-        <v>-5.231199411094171</v>
+        <v>-6.464245202651118</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.612251919463915</v>
       </c>
       <c r="E99">
-        <v>-42.00670888076782</v>
+        <v>-42.44571273649341</v>
       </c>
       <c r="F99">
-        <v>-4.492869445324965</v>
+        <v>-4.505883925590348</v>
       </c>
       <c r="G99">
-        <v>-5.862470787250098</v>
+        <v>-7.224250452647143</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.175105340833763</v>
       </c>
       <c r="E100">
-        <v>-44.1444814552278</v>
+        <v>-44.65789493161042</v>
       </c>
       <c r="F100">
-        <v>-4.76485394162535</v>
+        <v>-4.583462189597328</v>
       </c>
       <c r="G100">
-        <v>-6.558390496696911</v>
+        <v>-7.793915886862772</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.673978266300084</v>
       </c>
       <c r="E101">
-        <v>-45.83715937642187</v>
+        <v>-47.93005024499182</v>
       </c>
       <c r="F101">
-        <v>-5.0796153306063</v>
+        <v>-4.768104455313935</v>
       </c>
       <c r="G101">
-        <v>-7.092888005648863</v>
+        <v>-8.314244260906642</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.136434130838427</v>
       </c>
       <c r="E102">
-        <v>-47.73926789928566</v>
+        <v>-50.08656390913253</v>
       </c>
       <c r="F102">
-        <v>-4.97835321418588</v>
+        <v>-4.853159563498583</v>
       </c>
       <c r="G102">
-        <v>-7.844249421241852</v>
+        <v>-8.161287125355695</v>
       </c>
     </row>
   </sheetData>
